--- a/tame_output/ON/bt/strategyON_20240626.xlsx
+++ b/tame_output/ON/bt/strategyON_20240626.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.7%</t>
+          <t>-69.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.8%</t>
+          <t>447.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-533.2%</t>
+          <t>-521.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.6%</t>
+          <t>-163.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-8.5%</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>56.4%</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>-0.1</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-12.4%</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-210.2%</t>
+          <t>-219.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-198.6%</t>
+          <t>-179.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-62.0%</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783973</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919913</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883081</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074792</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242303</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367694</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879975</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502347</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675948</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539959</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496268</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577005</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.73583922294211</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430701</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.74322019600361</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508378</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417713</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205908</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225453</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264171</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742308</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.7535711658032</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809506</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472746</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798545</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498873</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705334</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190778</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913435</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532496</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793913</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011246</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898224</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509549</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476082</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319556</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397804</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024972</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863233</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947592</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326883</v>
+        <v>3.822707244326878</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314559</v>
+        <v>3.828837911314554</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690034</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674318</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163227</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022912</v>
+        <v>3.838228663022908</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042146</v>
+        <v>3.863924114042142</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078289</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232406</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162122</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639826</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274993</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393556</v>
+        <v>3.82869047939355</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714894</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175602</v>
+        <v>3.814259761756017</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654193</v>
+        <v>3.803426852654191</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717123</v>
+        <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702632</v>
+        <v>3.794453975702629</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539974</v>
+        <v>3.79560310053997</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389904</v>
+        <v>3.784700379389898</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534942</v>
+        <v>3.783234730534936</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77996275940168</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557228</v>
+        <v>3.769472653557226</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088383</v>
+        <v>3.766702530088381</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541377</v>
+        <v>3.76808110154137</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74395453947169</v>
+        <v>3.743954539471688</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.7191476609123</v>
+        <v>3.719147660912296</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.48019217795473</v>
+        <v>3.415373220060777</v>
       </c>
       <c r="C2006" t="n">
         <v>3.572486215072581</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.715834797898947</v>
+        <v>-3.602625967274921</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.085795871599255</v>
+        <v>2.131079403848865</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2537054161989548</v>
+        <v>0.446800105724055</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.724709464791954</v>
+        <v>3.840566278507014</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240626.xlsx
+++ b/tame_output/ON/bt/strategyON_20240626.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.0%</t>
+          <t>-69.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.4%</t>
+          <t>451.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.8%</t>
+          <t>-530.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.1%</t>
+          <t>-166.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,37 +1318,37 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-12.1%</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>55.7%</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-8.5%</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>56.4%</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>-0.1</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-219.3%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-172.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-179.3%</t>
+          <t>-195.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-62.0%</t>
+          <t>-71.7%</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.588698764279063</v>
+        <v>-4.555637566920171</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.033500857463208</v>
+        <v>1.046725336406765</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4744787570013713</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.584649533287758</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.543894592739133</v>
+        <v>-4.510833395380241</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.057431056476106</v>
+        <v>1.070655535419662</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4744787570013713</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.590658063684684</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.396151622504131</v>
+        <v>-4.363090425145239</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.195680892362128</v>
+        <v>1.208905371305685</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3066713997664881</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.770495125817635</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.498166305035352</v>
+        <v>-4.46510510767646</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.157668640881121</v>
+        <v>1.170893119824678</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3066713997664881</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.773288747349116</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.492013598982568</v>
+        <v>-4.458952401623676</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.160792071693893</v>
+        <v>1.17401655063745</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.3005186937137038</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.777642719372445</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.508822897133069</v>
+        <v>-4.475761699774178</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.153148829173803</v>
+        <v>1.166373308117359</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3173279918642055</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.766637617222254</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.446524898356947</v>
+        <v>-4.413463700998055</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.244403582481072</v>
+        <v>1.257628061424629</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3173279918642055</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.832973171019075</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.244734700691789</v>
+        <v>-4.211673503332897</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.033700533936534</v>
+        <v>1.04692501288009</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1193097996950511</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.660364958709966</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.171356603603053</v>
+        <v>-4.138295406244161</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.133342005094203</v>
+        <v>1.14656648403776</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.08018922680401847</v>
+        <v>-0.04593170260631452</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.754127534766761</v>
+        <v>2.774682049285383</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.269097148228028</v>
+        <v>-4.236035950869136</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.108873523360257</v>
+        <v>1.122098002303814</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09607850493699865</v>
+        <v>-0.06182098073929471</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.759221704003016</v>
+        <v>2.779776218521639</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.445434908350957</v>
+        <v>-4.412373710992065</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.036874400135757</v>
+        <v>1.050098879079314</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2381587408622241</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.65195502875393</v>
+        <v>2.672509543272553</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.36901286191903</v>
+        <v>-4.335951664560138</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.065934836748456</v>
+        <v>1.079159315692013</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2381587408622241</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.650446646793859</v>
+        <v>2.671001161312482</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.324639730280461</v>
+        <v>-4.291578532921569</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.08354695683932</v>
+        <v>1.096771435782877</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.1937856092236555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.676933393212436</v>
+        <v>2.697487907731059</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.316685759985689</v>
+        <v>-4.283624562626797</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.086728544957229</v>
+        <v>1.099953023900786</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.1937856092236555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.676933393212436</v>
+        <v>2.697487907731059</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.269030029424633</v>
+        <v>-4.235968832065741</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.112172594209456</v>
+        <v>1.125397073153013</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1803874028603038</v>
+        <v>-0.1461298786625999</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.711908588576875</v>
+        <v>2.732463103095497</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.168511870925879</v>
+        <v>-4.135450673566987</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.157272230983683</v>
+        <v>1.170496709927239</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.07986924436154924</v>
+        <v>-0.04561172016384529</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.777111857050852</v>
+        <v>2.797666371569474</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.229178461328267</v>
+        <v>-4.196117263969375</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.119760267298599</v>
+        <v>1.132984746242156</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1615675610800829</v>
+        <v>-0.127310036882379</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.714847539495604</v>
+        <v>2.735402054014227</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.184340059719869</v>
+        <v>-4.151278862360977</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.141793330552587</v>
+        <v>1.155017809496144</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1570241281352134</v>
+        <v>-0.1227666039375095</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.721671301873154</v>
+        <v>2.742225816391777</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.285098695476867</v>
+        <v>-4.252037498117975</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.105650815880866</v>
+        <v>1.118875294824423</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2458496968622189</v>
+        <v>-0.2115921726645149</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.672536900268029</v>
+        <v>2.693091414786652</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.240895858390966</v>
+        <v>-4.207834661032074</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.129211553243064</v>
+        <v>1.14243603218662</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2016468597763184</v>
+        <v>-0.1673893355786145</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.704938205047406</v>
+        <v>2.725492719566029</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022908</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.277874886054409</v>
+        <v>-4.244813688695517</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.112829942646934</v>
+        <v>1.126054421590491</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.1304154337872839</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.725532546591452</v>
+        <v>2.746087061110075</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042142</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.29793296491925</v>
+        <v>-4.264871767560358</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.156054476284037</v>
+        <v>1.169278955227594</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.1304154337872839</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.776780311774492</v>
+        <v>2.797334826293114</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.258002291741359</v>
+        <v>-4.224941094382467</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.170467450149447</v>
+        <v>1.183691929093003</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1247422848070975</v>
+        <v>-0.09048476060939359</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.799179420275479</v>
+        <v>2.819733934794102</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.206970199018832</v>
+        <v>-4.17390900165994</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.185828515476728</v>
+        <v>1.199052994420284</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.07371019208456958</v>
+        <v>-0.03945266788686563</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.824746904147266</v>
+        <v>2.845301418665888</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842576394162114</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.141746017891626</v>
+        <v>-4.108684820532734</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.229105592020315</v>
+        <v>1.242330070963872</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.008486010957363954</v>
+        <v>0.02577151324033999</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.881068816916295</v>
+        <v>2.901623331434917</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.104318997820492</v>
+        <v>-4.0712578004616</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.240037372348049</v>
+        <v>1.253261851291606</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.003234472928182297</v>
+        <v>0.03102305126952165</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.880180712033084</v>
+        <v>2.900735226551706</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.1244306538552</v>
+        <v>-4.091369456496309</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.233249502265406</v>
+        <v>1.246473981208962</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0077928720692369</v>
+        <v>0.04205039626694085</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.888053911362776</v>
+        <v>2.908608425881398</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82869047939355</v>
+        <v>3.828690479393548</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.070685839427996</v>
+        <v>-4.037624642069104</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.415305199057499</v>
+        <v>1.428529678001055</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.01785618150969887</v>
+        <v>0.05211370570740281</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.054649668048263</v>
+        <v>3.075204182566886</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714886</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.046894270821854</v>
+        <v>-4.013833073462962</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.544934735717773</v>
+        <v>1.558159214661329</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.0759052743135451</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.189037518429766</v>
+        <v>3.209592032948389</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756017</v>
+        <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.020810186558045</v>
+        <v>-3.987748989199154</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.547076345437155</v>
+        <v>1.560300824380711</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.0759052743135451</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.180745494443625</v>
+        <v>3.201300008962248</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654191</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.890517655628436</v>
+        <v>-3.857456458269544</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.597386553392778</v>
+        <v>1.610611032336335</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.278183374643576</v>
+        <v>0.3124408988412799</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.320860064744045</v>
+        <v>3.341414579262668</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79629317771712</v>
+        <v>3.796293177717119</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.881625194235152</v>
+        <v>-3.848563996876261</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.618497943676883</v>
+        <v>1.631722422620439</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.278183374643576</v>
+        <v>0.3124408988412799</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.338414470470837</v>
+        <v>3.358968984989459</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702629</v>
+        <v>3.794453975702628</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.050101311205029</v>
+        <v>-4.017040113846138</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.542962544293516</v>
+        <v>1.556187023237072</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2502355389269952</v>
+        <v>0.2844930631246991</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.313500816445472</v>
+        <v>3.334055330964095</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79560310053997</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.352301782343446</v>
+        <v>-3.319240584984555</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.803352053026011</v>
+        <v>1.816576531969567</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.2141450037542884</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.252561678011088</v>
+        <v>3.27311619252971</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389898</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.329580678660294</v>
+        <v>-3.296519481301403</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.803104516996177</v>
+        <v>1.816328995939733</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.2141450037542884</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.243225700507992</v>
+        <v>3.263780215026614</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534936</v>
+        <v>3.783234730534935</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.32785563537025</v>
+        <v>-3.294794438011359</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.962700660163363</v>
+        <v>1.975925139106919</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1816125228466282</v>
+        <v>0.2158700470443322</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.403166852333188</v>
+        <v>3.42372136685181</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401674</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.482636642148505</v>
+        <v>-3.449575444789614</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.937866079945707</v>
+        <v>1.951090558889264</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1482448487921521</v>
+        <v>0.1825023729898561</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.420224070394148</v>
+        <v>3.440778584912771</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.431201308763846</v>
+        <v>-3.398140111404955</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.955115569289116</v>
+        <v>1.968340048232673</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1996801821768118</v>
+        <v>0.2339377063745157</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.447760626414489</v>
+        <v>3.468315140933112</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088381</v>
+        <v>3.76670253008838</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.404250084437358</v>
+        <v>-3.371188887078467</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.975902212664453</v>
+        <v>1.98912669160801</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2488180524022349</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.466694987675862</v>
+        <v>3.487249502194485</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.540203092493674</v>
+        <v>-3.507141895134783</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.105624141586887</v>
+        <v>2.118848620530443</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2488180524022349</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.650798119820822</v>
+        <v>3.671352634339445</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471688</v>
+        <v>3.743954539471687</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.562611210298546</v>
+        <v>-3.529550012939655</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.088777589367931</v>
+        <v>2.102002068311487</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2488180524022349</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.642914814723815</v>
+        <v>3.663469329242438</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912296</v>
+        <v>3.719147660912295</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.710616977777946</v>
+        <v>-3.677555780419055</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.031629281925809</v>
+        <v>2.044853760869365</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1278335193409895</v>
+        <v>0.1620910435386934</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.592932608955328</v>
+        <v>3.61348712347395</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.415373220060777</v>
+        <v>3.796491864476948</v>
       </c>
       <c r="C2006" t="n">
         <v>3.572486215072581</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.602625967274921</v>
+        <v>-3.686996706307585</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.131079403848865</v>
+        <v>2.0973311082358</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.446800105724055</v>
+        <v>0.2845181610820848</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.840566278507014</v>
+        <v>3.743197111721832</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240626.xlsx
+++ b/tame_output/ON/bt/strategyON_20240626.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-68.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.7%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-530.3%</t>
+          <t>-517.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.5%</t>
+          <t>-161.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-209.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.5%</t>
+          <t>-170.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.5%</t>
+          <t>-199.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-73.8%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987906</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577002</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003607</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508374</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417707</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472742</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.68959784049887</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729275</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.74117406991343</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.555637566920171</v>
+        <v>-4.588698764279063</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.046725336406765</v>
+        <v>1.033500857463208</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4744787570013713</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.584649533287758</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789128</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.510833395380241</v>
+        <v>-4.543894592739133</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.070655535419662</v>
+        <v>1.057431056476106</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4744787570013713</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.590658063684684</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.363090425145239</v>
+        <v>-4.396151622504131</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.208905371305685</v>
+        <v>1.195680892362128</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3066713997664881</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.770495125817635</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.46510510767646</v>
+        <v>-4.498166305035352</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.170893119824678</v>
+        <v>1.157668640881121</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3066713997664881</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.773288747349116</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.458952401623676</v>
+        <v>-4.492013598982568</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.17401655063745</v>
+        <v>1.160792071693893</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3005186937137038</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.777642719372445</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.475761699774178</v>
+        <v>-4.508822897133069</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.166373308117359</v>
+        <v>1.153148829173803</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3173279918642055</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.766637617222254</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.413463700998055</v>
+        <v>-4.446524898356947</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.257628061424629</v>
+        <v>1.244403582481072</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3173279918642055</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.832973171019075</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.211673503332897</v>
+        <v>-4.244734700691789</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.04692501288009</v>
+        <v>1.033700533936534</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1193097996950511</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.660364958709966</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.138295406244161</v>
+        <v>-4.171356603603053</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.14656648403776</v>
+        <v>1.133342005094203</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.04593170260631452</v>
+        <v>-0.08018922680401847</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.774682049285383</v>
+        <v>2.754127534766761</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.236035950869136</v>
+        <v>-4.269097148228028</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.122098002303814</v>
+        <v>1.108873523360257</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.06182098073929471</v>
+        <v>-0.09607850493699865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.779776218521639</v>
+        <v>2.759221704003016</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.412373710992065</v>
+        <v>-4.445434908350957</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.050098879079314</v>
+        <v>1.036874400135757</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2381587408622241</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.672509543272553</v>
+        <v>2.65195502875393</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.335951664560138</v>
+        <v>-4.36901286191903</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.079159315692013</v>
+        <v>1.065934836748456</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2381587408622241</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.671001161312482</v>
+        <v>2.650446646793859</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.291578532921569</v>
+        <v>-4.324639730280461</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.096771435782877</v>
+        <v>1.08354695683932</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1937856092236555</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.697487907731059</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.283624562626797</v>
+        <v>-4.316685759985689</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.099953023900786</v>
+        <v>1.086728544957229</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1937856092236555</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.697487907731059</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.235968832065741</v>
+        <v>-4.269030029424633</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.125397073153013</v>
+        <v>1.112172594209456</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1461298786625999</v>
+        <v>-0.1803874028603038</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.732463103095497</v>
+        <v>2.711908588576875</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.135450673566987</v>
+        <v>-4.168511870925879</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.170496709927239</v>
+        <v>1.157272230983683</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.04561172016384529</v>
+        <v>-0.07986924436154924</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.797666371569474</v>
+        <v>2.777111857050852</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.196117263969375</v>
+        <v>-4.229178461328267</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.132984746242156</v>
+        <v>1.119760267298599</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.127310036882379</v>
+        <v>-0.1615675610800829</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.735402054014227</v>
+        <v>2.714847539495604</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.151278862360977</v>
+        <v>-4.184340059719869</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.155017809496144</v>
+        <v>1.141793330552587</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1227666039375095</v>
+        <v>-0.1570241281352134</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742225816391777</v>
+        <v>2.721671301873154</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.252037498117975</v>
+        <v>-4.285098695476867</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.118875294824423</v>
+        <v>1.105650815880866</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2115921726645149</v>
+        <v>-0.2458496968622189</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.693091414786652</v>
+        <v>2.672536900268029</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.207834661032074</v>
+        <v>-4.240895858390966</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.14243603218662</v>
+        <v>1.129211553243064</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1673893355786145</v>
+        <v>-0.2016468597763184</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.725492719566029</v>
+        <v>2.704938205047406</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.244813688695517</v>
+        <v>-4.277874886054409</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.126054421590491</v>
+        <v>1.112829942646934</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1304154337872839</v>
+        <v>-0.1646729579849879</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.746087061110075</v>
+        <v>2.725532546591452</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.264871767560358</v>
+        <v>-4.29793296491925</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.169278955227594</v>
+        <v>1.156054476284037</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1304154337872839</v>
+        <v>-0.1646729579849879</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.797334826293114</v>
+        <v>2.776780311774492</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078283</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.224941094382467</v>
+        <v>-4.258002291741359</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.183691929093003</v>
+        <v>1.170467450149447</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.09048476060939359</v>
+        <v>-0.1247422848070975</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.819733934794102</v>
+        <v>2.799179420275479</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.17390900165994</v>
+        <v>-4.206970199018832</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.199052994420284</v>
+        <v>1.185828515476728</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.03945266788686563</v>
+        <v>-0.07371019208456958</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.845301418665888</v>
+        <v>2.824746904147266</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.108684820532734</v>
+        <v>-4.141746017891626</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.242330070963872</v>
+        <v>1.229105592020315</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.02577151324033999</v>
+        <v>-0.008486010957363954</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.901623331434917</v>
+        <v>2.881068816916295</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.0712578004616</v>
+        <v>-4.104318997820492</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.253261851291606</v>
+        <v>1.240037372348049</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.03102305126952165</v>
+        <v>-0.003234472928182297</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.900735226551706</v>
+        <v>2.880180712033084</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.091369456496309</v>
+        <v>-4.1244306538552</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.246473981208962</v>
+        <v>1.233249502265406</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.04205039626694085</v>
+        <v>0.0077928720692369</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.908608425881398</v>
+        <v>2.888053911362776</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.037624642069104</v>
+        <v>-4.070685839427996</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.428529678001055</v>
+        <v>1.415305199057499</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.05211370570740281</v>
+        <v>0.01785618150969887</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.075204182566886</v>
+        <v>3.054649668048263</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714886</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.013833073462962</v>
+        <v>-4.046894270821854</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.558159214661329</v>
+        <v>1.544934735717773</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.0759052743135451</v>
+        <v>0.04164775011584115</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.209592032948389</v>
+        <v>3.189037518429766</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.987748989199154</v>
+        <v>-4.020810186558045</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.560300824380711</v>
+        <v>1.547076345437155</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.0759052743135451</v>
+        <v>0.04164775011584115</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.201300008962248</v>
+        <v>3.180745494443625</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654189</v>
+        <v>3.803426852654188</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.857456458269544</v>
+        <v>-3.890517655628436</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.610611032336335</v>
+        <v>1.597386553392778</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3124408988412799</v>
+        <v>0.278183374643576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.341414579262668</v>
+        <v>3.320860064744045</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717119</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.848563996876261</v>
+        <v>-3.881625194235152</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.631722422620439</v>
+        <v>1.618497943676883</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3124408988412799</v>
+        <v>0.278183374643576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.358968984989459</v>
+        <v>3.338414470470837</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702628</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.017040113846138</v>
+        <v>-4.050101311205029</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.556187023237072</v>
+        <v>1.542962544293516</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2844930631246991</v>
+        <v>0.2502355389269952</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.334055330964095</v>
+        <v>3.313500816445472</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539968</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.319240584984555</v>
+        <v>-3.352301782343446</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.816576531969567</v>
+        <v>1.803352053026011</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2141450037542884</v>
+        <v>0.1798874795565845</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.27311619252971</v>
+        <v>3.252561678011088</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389897</v>
+        <v>3.784700379389896</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.296519481301403</v>
+        <v>-3.329580678660294</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.816328995939733</v>
+        <v>1.803104516996177</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2141450037542884</v>
+        <v>0.1798874795565845</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.263780215026614</v>
+        <v>3.243225700507992</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.294794438011359</v>
+        <v>-3.32785563537025</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.975925139106919</v>
+        <v>1.962700660163363</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2158700470443322</v>
+        <v>0.1816125228466282</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.42372136685181</v>
+        <v>3.403166852333188</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401674</v>
+        <v>3.779962759401673</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.449575444789614</v>
+        <v>-3.482636642148505</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.951090558889264</v>
+        <v>1.937866079945707</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1825023729898561</v>
+        <v>0.1482448487921521</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.440778584912771</v>
+        <v>3.420224070394148</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557226</v>
+        <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.398140111404955</v>
+        <v>-3.431201308763846</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.968340048232673</v>
+        <v>1.955115569289116</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2339377063745157</v>
+        <v>0.1996801821768118</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.468315140933112</v>
+        <v>3.447760626414489</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76670253008838</v>
+        <v>3.766702530088378</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.371188887078467</v>
+        <v>-3.404250084437358</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.98912669160801</v>
+        <v>1.975902212664453</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2488180524022349</v>
+        <v>0.2145605282045309</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.487249502194485</v>
+        <v>3.466694987675862</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76808110154137</v>
+        <v>3.768081101541369</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.507141895134783</v>
+        <v>-3.374977463418289</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.118848620530443</v>
+        <v>2.171714393217041</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2488180524022349</v>
+        <v>0.2145605282045309</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.671352634339445</v>
+        <v>3.650798119820822</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471687</v>
+        <v>3.743954539471685</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.529550012939655</v>
+        <v>-3.397385581223161</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.102002068311487</v>
+        <v>2.154867840998085</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2488180524022349</v>
+        <v>0.2145605282045309</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.663469329242438</v>
+        <v>3.642914814723815</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912295</v>
+        <v>3.719147660912294</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.677555780419055</v>
+        <v>-3.54539134870256</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.044853760869365</v>
+        <v>2.097719533555963</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1620910435386934</v>
+        <v>0.1278335193409895</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.61348712347395</v>
+        <v>3.592932608955328</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.796491864476948</v>
+        <v>3.748695841503036</v>
       </c>
       <c r="C2006" t="n">
         <v>3.572486215072581</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.686996706307585</v>
+        <v>-3.55483227459109</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.0973311082358</v>
+        <v>2.150196880922398</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2845181610820848</v>
+        <v>0.2502606368843809</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.743197111721832</v>
+        <v>3.72264259720321</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240626.xlsx
+++ b/tame_output/ON/bt/strategyON_20240626.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>452.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-517.1%</t>
+          <t>-497.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-153.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-209.8%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-170.0%</t>
+          <t>-172.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-199.0%</t>
+          <t>-195.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2006"/>
+  <dimension ref="A1:G2007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388731</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626477</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987906</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279188</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883077</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242297</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502342</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675943</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577002</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674519</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003607</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508374</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417707</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.76526135305532</v>
+        <v>-4.611876276224752</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9188984342366964</v>
+        <v>0.9802524649689235</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.589787093262851</v>
+        <v>-4.436402016432282</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9936553701454718</v>
+        <v>1.055009400877699</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.7007233459041</v>
+        <v>-4.547338269073531</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9250228978501793</v>
+        <v>0.9863769285824067</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.667059800431818</v>
+        <v>-4.513674723601249</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9416197012589977</v>
+        <v>1.002973731991225</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.607207181228095</v>
+        <v>-4.453822104397526</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9757331353726193</v>
+        <v>1.037087166104847</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.520963718201717</v>
+        <v>-4.367578641371148</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.005176791157031</v>
+        <v>1.066530821889258</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.566270537600697</v>
+        <v>-4.412885460770128</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9788298388419643</v>
+        <v>1.040183869574192</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.595303642302998</v>
+        <v>-4.441918565472429</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9677684699941453</v>
+        <v>1.029122500726373</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.502493160852138</v>
+        <v>-4.349108084021569</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.934165354465855</v>
+        <v>0.9955193851980824</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.546882630181566</v>
+        <v>-4.393497553350997</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9182830426586848</v>
+        <v>0.9796370733909123</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472742</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.434211411945316</v>
+        <v>-4.280826335114747</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9584272384649077</v>
+        <v>1.019781269197135</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798542</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.321834410762643</v>
+        <v>-4.168449333932074</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.008869334768644</v>
+        <v>1.070223365500872</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049887</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.349614808663995</v>
+        <v>-4.196229731833427</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.009254377376642</v>
+        <v>1.07060840810887</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.432616089689274</v>
+        <v>-4.279231012858705</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.814409584967184</v>
+        <v>0.8757636156994115</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729275</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.541230168132605</v>
+        <v>-4.387845091302037</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8911136143090572</v>
+        <v>0.9524676450412846</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190773</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.505821129884462</v>
+        <v>-4.352436053053894</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9197902557106372</v>
+        <v>0.9811442864428648</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991343</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.467437467326311</v>
+        <v>-4.314052390495743</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9325631620762664</v>
+        <v>0.9939171928084938</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.290321137291145</v>
+        <v>-4.136936060460576</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.000138722935635</v>
+        <v>1.061492753667862</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.335413382124691</v>
+        <v>-4.182028305294122</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9827852167641296</v>
+        <v>1.044139247496357</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.156037960885923</v>
+        <v>-4.002652884055355</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.048322360566051</v>
+        <v>1.109676391298279</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982234</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.201052174406529</v>
+        <v>-4.04766709757596</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.011124130489399</v>
+        <v>1.072478161221626</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.468056684678964</v>
+        <v>-4.314671607848395</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9100138887193703</v>
+        <v>0.9713679194515976</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.569254466116137</v>
+        <v>-4.415869389285568</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8687386980410026</v>
+        <v>0.9300927287732299</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.562743499501824</v>
+        <v>-4.409358422671255</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8689430462410443</v>
+        <v>0.9302970769732717</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.543705371794527</v>
+        <v>-4.390320294963958</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8730830165322081</v>
+        <v>0.9344370472644357</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.574832002945145</v>
+        <v>-4.421446926114577</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.038214233010641</v>
+        <v>1.099568263742869</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.588698764279063</v>
+        <v>-4.397987167089279</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.033500857463208</v>
+        <v>1.109785496339121</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4725063937754383</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.585832951223317</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789128</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.543894592739133</v>
+        <v>-4.353182995549349</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.057431056476106</v>
+        <v>1.133715695352019</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4725063937754383</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.591841481620243</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.396151622504131</v>
+        <v>-4.205440025314346</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.195680892362128</v>
+        <v>1.271965531238042</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3046990365405552</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.771678543753195</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.498166305035352</v>
+        <v>-4.307454707845568</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.157668640881121</v>
+        <v>1.233953279757035</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3046990365405552</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.774472165284676</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.492013598982568</v>
+        <v>-4.301302001792783</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.160792071693893</v>
+        <v>1.237076710569807</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.2985463304877709</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.778826137308005</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.508822897133069</v>
+        <v>-4.318111299943285</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.153148829173803</v>
+        <v>1.229433468049716</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3153556286382725</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.767821035157815</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.446524898356947</v>
+        <v>-4.255813301167163</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.244403582481072</v>
+        <v>1.320688221356986</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3153556286382725</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.834156588954635</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.244734700691789</v>
+        <v>-4.054023103502005</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.033700533936534</v>
+        <v>1.109985172812447</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1173374364691182</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.661548376645526</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.171356603603053</v>
+        <v>-3.980645006413269</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.133342005094203</v>
+        <v>1.209626643970117</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.08018922680401847</v>
+        <v>-0.0439593393803816</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.754127534766761</v>
+        <v>2.775865467220943</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.269097148228028</v>
+        <v>-4.078385551038243</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.108873523360257</v>
+        <v>1.185158162236171</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09607850493699865</v>
+        <v>-0.05984861751336179</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.759221704003016</v>
+        <v>2.780959636457199</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.445434908350957</v>
+        <v>-4.254723311161172</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.036874400135757</v>
+        <v>1.113159039011671</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2361863776362912</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.65195502875393</v>
+        <v>2.673692961208113</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.36901286191903</v>
+        <v>-4.178301264729245</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.065934836748456</v>
+        <v>1.14221947562437</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2361863776362912</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.650446646793859</v>
+        <v>2.672184579248041</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.324639730280461</v>
+        <v>-4.133928133090676</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.08354695683932</v>
+        <v>1.159831595715234</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.1918132459977226</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.676933393212436</v>
+        <v>2.698671325666619</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.316685759985689</v>
+        <v>-4.125974162795904</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.086728544957229</v>
+        <v>1.163013183833143</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.1918132459977226</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.676933393212436</v>
+        <v>2.698671325666619</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.269030029424633</v>
+        <v>-4.078318432234848</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.112172594209456</v>
+        <v>1.18845723308537</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1803874028603038</v>
+        <v>-0.1441575154366669</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.711908588576875</v>
+        <v>2.733646521031057</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.168511870925879</v>
+        <v>-3.977800273736094</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.157272230983683</v>
+        <v>1.233556869859597</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.07986924436154924</v>
+        <v>-0.04363935693791238</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.777111857050852</v>
+        <v>2.798849789505034</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.229178461328267</v>
+        <v>-4.038466864138483</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.119760267298599</v>
+        <v>1.196044906174513</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1615675610800829</v>
+        <v>-0.125337673656446</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.714847539495604</v>
+        <v>2.736585471949786</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.184340059719869</v>
+        <v>-3.993628462530085</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.141793330552587</v>
+        <v>1.218077969428501</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1570241281352134</v>
+        <v>-0.1207942407115766</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.721671301873154</v>
+        <v>2.743409234327336</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674312</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.285098695476867</v>
+        <v>-4.094387098287084</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.105650815880866</v>
+        <v>1.18193545475678</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2458496968622189</v>
+        <v>-0.209619809438582</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.672536900268029</v>
+        <v>2.694274832722211</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.240895858390966</v>
+        <v>-4.050184261201183</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.129211553243064</v>
+        <v>1.205496192118977</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2016468597763184</v>
+        <v>-0.1654169723526815</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.704938205047406</v>
+        <v>2.726676137501589</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.277874886054409</v>
+        <v>-4.087163288864627</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.112829942646934</v>
+        <v>1.189114581522847</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.128443070561351</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.725532546591452</v>
+        <v>2.747270479045635</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.29793296491925</v>
+        <v>-4.107221367729467</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.156054476284037</v>
+        <v>1.23233911515995</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.128443070561351</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.776780311774492</v>
+        <v>2.798518244228674</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078283</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.258002291741359</v>
+        <v>-4.067290694551577</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.170467450149447</v>
+        <v>1.24675208902536</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1247422848070975</v>
+        <v>-0.08851239738346067</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.799179420275479</v>
+        <v>2.820917352729662</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.206970199018832</v>
+        <v>-4.016258601829049</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.185828515476728</v>
+        <v>1.262113154352641</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.07371019208456958</v>
+        <v>-0.03748030466093272</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.824746904147266</v>
+        <v>2.846484836601448</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.141746017891626</v>
+        <v>-3.951034420701844</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.229105592020315</v>
+        <v>1.305390230896228</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.008486010957363954</v>
+        <v>0.02774387646627291</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.881068816916295</v>
+        <v>2.902806749370476</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.104318997820492</v>
+        <v>-3.91360740063071</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.240037372348049</v>
+        <v>1.316322011223962</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.003234472928182297</v>
+        <v>0.03299541449545457</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.880180712033084</v>
+        <v>2.901918644487266</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.1244306538552</v>
+        <v>-3.933719056665419</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.233249502265406</v>
+        <v>1.309534141141319</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0077928720692369</v>
+        <v>0.04402275949287376</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.888053911362776</v>
+        <v>2.909791843816958</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.070685839427996</v>
+        <v>-3.879974242238214</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.415305199057499</v>
+        <v>1.491589837933411</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.01785618150969887</v>
+        <v>0.05408606893333573</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.054649668048263</v>
+        <v>3.076387600502446</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714886</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.046894270821854</v>
+        <v>-3.856182673632071</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.544934735717773</v>
+        <v>1.621219374593685</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.07787763753947802</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.189037518429766</v>
+        <v>3.210775450883948</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.020810186558045</v>
+        <v>-3.830098589368264</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.547076345437155</v>
+        <v>1.623360984313067</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.07787763753947802</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.180745494443625</v>
+        <v>3.202483426897807</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654188</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.890517655628436</v>
+        <v>-3.699806058438654</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.597386553392778</v>
+        <v>1.673671192268691</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.278183374643576</v>
+        <v>0.3144132620672128</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.320860064744045</v>
+        <v>3.342597997198228</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.881625194235152</v>
+        <v>-3.690913597045371</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.618497943676883</v>
+        <v>1.694782582552796</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.278183374643576</v>
+        <v>0.3144132620672128</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.338414470470837</v>
+        <v>3.360152402925019</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.050101311205029</v>
+        <v>-3.859389714015248</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.542962544293516</v>
+        <v>1.619247183169428</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2502355389269952</v>
+        <v>0.286465426350632</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.313500816445472</v>
+        <v>3.335238748899654</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.352301782343446</v>
+        <v>-3.161590185153665</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.803352053026011</v>
+        <v>1.879636691901923</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.2161173669802213</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.252561678011088</v>
+        <v>3.27429961046527</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.329580678660294</v>
+        <v>-3.138869081470513</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.803104516996177</v>
+        <v>1.879389155872089</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.2161173669802213</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.243225700507992</v>
+        <v>3.264963632962175</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534935</v>
+        <v>3.783234730534934</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.32785563537025</v>
+        <v>-3.137144038180469</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.962700660163363</v>
+        <v>2.038985299039275</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1816125228466282</v>
+        <v>0.2178424102702651</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.403166852333188</v>
+        <v>3.424904784787369</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.482636642148505</v>
+        <v>-3.291925044958724</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.937866079945707</v>
+        <v>2.01415071882162</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1482448487921521</v>
+        <v>0.184474736215789</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.420224070394148</v>
+        <v>3.441962002848331</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557225</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.431201308763846</v>
+        <v>-3.240489711574064</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.955115569289116</v>
+        <v>2.031400208165029</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1996801821768118</v>
+        <v>0.2359100696004486</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.447760626414489</v>
+        <v>3.469498558868672</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088378</v>
+        <v>3.766702530088379</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.404250084437358</v>
+        <v>-3.213538487247576</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.975902212664453</v>
+        <v>2.052186851540366</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2507904156281678</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.466694987675862</v>
+        <v>3.488432920130045</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.374977463418289</v>
+        <v>-3.178502002147465</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.171714393217041</v>
+        <v>2.250304577725371</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2507904156281678</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.650798119820822</v>
+        <v>3.672536052275004</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471685</v>
+        <v>3.743954539471686</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.397385581223161</v>
+        <v>-3.200910119952337</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.154867840998085</v>
+        <v>2.233458025506414</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2507904156281678</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.642914814723815</v>
+        <v>3.664652747177997</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.54539134870256</v>
+        <v>-3.348915887431736</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.097719533555963</v>
+        <v>2.176309718064292</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1278335193409895</v>
+        <v>0.1640634067646263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.592932608955328</v>
+        <v>3.61467054140951</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,45 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.748695841503036</v>
+        <v>3.729481318919242</v>
       </c>
       <c r="C2006" t="n">
         <v>3.572486215072581</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.55483227459109</v>
+        <v>-3.358356813320266</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.150196880922398</v>
+        <v>2.228787065430728</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2502606368843809</v>
+        <v>0.2864905243080177</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.72264259720321</v>
+        <v>3.744380529657392</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="2" t="n">
+        <v>45469</v>
+      </c>
+      <c r="B2007" t="n">
+        <v>3.758348826980376</v>
+      </c>
+      <c r="C2007" t="n">
+        <v>3.692841438568102</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>-3.358356813320266</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>2.228787065430728</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>0.2864905243080177</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>3.68590523555447</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240626.xlsx
+++ b/tame_output/ON/bt/strategyON_20240626.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.3%</t>
+          <t>447.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-497.4%</t>
+          <t>-522.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>162.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.3%</t>
+          <t>-163.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.8%</t>
+          <t>-167.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.3%</t>
+          <t>-205.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.352766700288008</v>
+        <v>-7.420182573667817</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1671568985950591</v>
+        <v>0.1401905492431355</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.597038101015078</v>
+        <v>-7.664453974394887</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07970702897291027</v>
+        <v>0.05274067962098661</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.802289120251838</v>
+        <v>-7.869704993631647</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.006293813576098817</v>
+        <v>-0.03326016292802203</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.965868998436221</v>
+        <v>-8.033284871816031</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07332084479485124</v>
+        <v>-0.1002871941467749</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.262530340246419</v>
+        <v>-8.329946213626229</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1882064055897223</v>
+        <v>-0.215172754941646</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.449250048555722</v>
+        <v>-8.516665921935532</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2669205934478462</v>
+        <v>-0.2938869427997703</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.832251437298353</v>
+        <v>-8.899667310678163</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4202232502664831</v>
+        <v>-0.4471895996184068</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.014121228283388</v>
+        <v>-9.081537101663198</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4903996506890667</v>
+        <v>-0.5173660000409908</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.37365155078739</v>
+        <v>-9.441067424167199</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.628861476392617</v>
+        <v>-0.6558278257445411</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.424000614241612</v>
+        <v>-9.491416487621422</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6410850818171285</v>
+        <v>-0.6680514311690522</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.521619891663008</v>
+        <v>-9.589035765042818</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.677091042163918</v>
+        <v>-0.7040573915158421</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.669145979668651</v>
+        <v>-9.73656185304846</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.733207921044603</v>
+        <v>-0.7601742703965271</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.873404154998514</v>
+        <v>-9.940820028378324</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8093979940579059</v>
+        <v>-0.83636434340983</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.947737131258679</v>
+        <v>-10.01515300463849</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.834648630077536</v>
+        <v>-0.8616149794294601</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.87426729959123</v>
+        <v>-9.94168317297104</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7898889959171349</v>
+        <v>-0.816855345269059</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.04939171697777</v>
+        <v>-10.11680759035758</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8453835421242353</v>
+        <v>-0.8723498914761594</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.28384381099226</v>
+        <v>-10.35125968437207</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9463835446316273</v>
+        <v>-0.9733498939835514</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.38821854201871</v>
+        <v>-10.45563441539852</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9948056278161821</v>
+        <v>-1.021771977168106</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.44100469761904</v>
+        <v>-10.50842057099885</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.014804300217756</v>
+        <v>-1.04177064956968</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.56704149098733</v>
+        <v>-10.63445736436713</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.062525288935957</v>
+        <v>-1.089491638287881</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.51502597701851</v>
+        <v>-10.58244185039832</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.037728747662031</v>
+        <v>-1.064695097013955</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.65669781874263</v>
+        <v>-10.72411369212244</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.095872711250421</v>
+        <v>-1.122839060602345</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.6071069743178</v>
+        <v>-10.67452284769761</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.060982963315615</v>
+        <v>-1.087949312667539</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.59429958131302</v>
+        <v>-10.66171545469283</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.068911139760389</v>
+        <v>-1.095877489112313</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.36845442859361</v>
+        <v>-10.43587030197342</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9689940056364157</v>
+        <v>-0.9959603549883398</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.24387577225602</v>
+        <v>-10.31129164563583</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9180233985453197</v>
+        <v>-0.9449897478972447</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.29677106030031</v>
+        <v>-10.36418693368012</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9365477396009263</v>
+        <v>-0.9635140889528513</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.22463788501243</v>
+        <v>-10.29205375839224</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9019607652471375</v>
+        <v>-0.9289271145990625</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.15327149240278</v>
+        <v>-10.22068736578259</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8831514705971442</v>
+        <v>-0.9101178199490683</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.05981245841755</v>
+        <v>-10.12722833179737</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8556513383159614</v>
+        <v>-0.8826176876678864</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436232</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.792570657549156</v>
+        <v>-9.859986530928968</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7505891784679766</v>
+        <v>-0.7775555278199011</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.694663618872665</v>
+        <v>-9.762079492252477</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7117266779708409</v>
+        <v>-0.7386930273227654</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097247</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.670710077896707</v>
+        <v>-9.738125951276519</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7014767554349643</v>
+        <v>-0.7284431047868889</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.406650139573911</v>
+        <v>-9.474066012953722</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6091130962675977</v>
+        <v>-0.6360794456195222</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.699570516069073</v>
+        <v>-8.766986389448885</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3290682805259637</v>
+        <v>-0.3560346298778883</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.659386217702883</v>
+        <v>-8.726802091082694</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3126509372916462</v>
+        <v>-0.3396172866435707</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.495986346763519</v>
+        <v>-8.563402220143331</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2479241676951438</v>
+        <v>-0.2748905170470684</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.26250512453392</v>
+        <v>-8.329920997913732</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1466072499654514</v>
+        <v>-0.1735735993173764</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.112838733526406</v>
+        <v>-8.180254606906217</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.08963290387540512</v>
+        <v>-0.1165992532273297</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.980563259895519</v>
+        <v>-8.04797913327533</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.04135522767602362</v>
+        <v>-0.06832157702794772</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.824824927335778</v>
+        <v>-7.892240800715588</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.0237551660355102</v>
+        <v>-0.003211183316414346</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.575825128652196</v>
+        <v>-7.643241002032007</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.136261426732601</v>
+        <v>0.1092950773806769</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.681415118425301</v>
+        <v>-7.748830991805112</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03395049877585921</v>
+        <v>-0.06091684812778375</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987906</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.700150020543898</v>
+        <v>-7.767565893923709</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.007099882253788437</v>
+        <v>-0.01986646709813611</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.552209979136299</v>
+        <v>-7.619625852516109</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05360302387133942</v>
+        <v>-0.08056937322326396</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.49924045688231</v>
+        <v>-7.566656330262121</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04112920122322228</v>
+        <v>-0.06809555057514682</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.45569205011162</v>
+        <v>-7.52310792349143</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03067045061003926</v>
+        <v>-0.0576367999619638</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.213543656657762</v>
+        <v>-7.280959530037572</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08065126115264709</v>
+        <v>0.05368491180072255</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.10528451953524</v>
+        <v>-7.172700392915051</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1184870364608508</v>
+        <v>0.09152068710892625</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.981993384718109</v>
+        <v>-7.04940925809792</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1653015843982799</v>
+        <v>0.1383352350463558</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.960844185814666</v>
+        <v>-7.028260059194476</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1814622421969823</v>
+        <v>0.1544958928450582</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.717078743831221</v>
+        <v>-6.784494617211032</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2747491273374107</v>
+        <v>0.2477827779854866</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.615315923553927</v>
+        <v>-6.682731796933737</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3175785693683446</v>
+        <v>0.2906122200164205</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.365465529604852</v>
+        <v>-6.432881402984663</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4102608019316767</v>
+        <v>0.3832944525797526</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.189573437137419</v>
+        <v>-6.256989310517231</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4842167624392988</v>
+        <v>0.4572504130873742</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.018126974114955</v>
+        <v>-6.085542847494767</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5661228537028378</v>
+        <v>0.5391565043509132</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.943837408376616</v>
+        <v>-6.011253281756428</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5948591576144704</v>
+        <v>0.5678928082625458</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883078</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.880201666142682</v>
+        <v>-5.947617539522494</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6250082555623617</v>
+        <v>0.5980419062104367</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.768774906816762</v>
+        <v>-5.836190780196573</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6507732180765253</v>
+        <v>0.6238068687246008</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.7976948842423</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.528344410011901</v>
+        <v>-5.595760283391713</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7486884934233466</v>
+        <v>0.7217221440714221</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936769</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.456101841840707</v>
+        <v>-5.523517715220518</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7815148345266447</v>
+        <v>0.7545484851747202</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.403103519559319</v>
+        <v>-5.47051939293913</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8033927473565399</v>
+        <v>0.7764263980046153</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502344</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.294298634079592</v>
+        <v>-5.361714507459403</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8439127727684244</v>
+        <v>0.8169464234164998</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675946</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.074277836042581</v>
+        <v>-5.141693709422393</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9335001289938427</v>
+        <v>0.9065337796419182</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539957</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.941410146979304</v>
+        <v>-5.008826020359115</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.002541387420977</v>
+        <v>0.9755750380690524</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.821237063614805</v>
+        <v>-4.888652936994617</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.051756465207078</v>
+        <v>1.024790115855154</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.676564918515068</v>
+        <v>-4.743980791894879</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.119713425808413</v>
+        <v>1.092747076456489</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73643974587276</v>
+        <v>-4.803855619252571</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.081800986266762</v>
+        <v>1.054834636914837</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.649640248093752</v>
+        <v>-4.717056121473563</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138921278700932</v>
+        <v>1.111954929349007</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.652109954555558</v>
+        <v>-4.719525827935369</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.138005797489621</v>
+        <v>1.111039448137697</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003606</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.720480140879568</v>
+        <v>-4.787896014259379</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.121664645434719</v>
+        <v>1.094698296082794</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508374</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.734268193726614</v>
+        <v>-4.801684067106426</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.106586132927792</v>
+        <v>1.079619783575867</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417709</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.611876276224752</v>
+        <v>-4.832677226435131</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9802524649689235</v>
+        <v>0.8919320848847718</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.436402016432282</v>
+        <v>-4.657202966642663</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.055009400877699</v>
+        <v>0.966689020793547</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.76502432322545</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.547338269073531</v>
+        <v>-4.768139219283912</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9863769285824067</v>
+        <v>0.8980565484982546</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.513674723601249</v>
+        <v>-4.734475673811629</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.002973731991225</v>
+        <v>0.914653351907073</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.453822104397526</v>
+        <v>-4.674623054607906</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.037087166104847</v>
+        <v>0.9487667860206948</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.367578641371148</v>
+        <v>-4.588379591581528</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.066530821889258</v>
+        <v>0.9782104418051061</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.412885460770128</v>
+        <v>-4.633686410980508</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.040183869574192</v>
+        <v>0.9518634894900397</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.441918565472429</v>
+        <v>-4.662719515682809</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.029122500726373</v>
+        <v>0.9408021206422208</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.349108084021569</v>
+        <v>-4.56990903423195</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9955193851980824</v>
+        <v>0.9071990051139303</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.393497553350997</v>
+        <v>-4.614298503561377</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9796370733909123</v>
+        <v>0.8913166933067602</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472742</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.280826335114747</v>
+        <v>-4.501627285325127</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.019781269197135</v>
+        <v>0.9314608891129832</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.168449333932074</v>
+        <v>-4.389250284142454</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.070223365500872</v>
+        <v>0.9819029854167196</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.68959784049887</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.196229731833427</v>
+        <v>-4.417030682043807</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.07060840810887</v>
+        <v>0.9822880280247177</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.279231012858705</v>
+        <v>-4.500031963069086</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8757636156994115</v>
+        <v>0.7874432356152594</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729275</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.387845091302037</v>
+        <v>-4.608646041512417</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9524676450412846</v>
+        <v>0.8641472649571325</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190774</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.352436053053894</v>
+        <v>-4.573237003264274</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9811442864428648</v>
+        <v>0.8928239063587127</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.314052390495743</v>
+        <v>-4.534853340706123</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9939171928084938</v>
+        <v>0.9055968127243417</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532492</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.136936060460576</v>
+        <v>-4.357737010670957</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.061492753667862</v>
+        <v>0.9731723735837101</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.74132844879391</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.182028305294122</v>
+        <v>-4.402829255504503</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.044139247496357</v>
+        <v>0.955818867412205</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011242</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.002652884055355</v>
+        <v>-4.345995305886128</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.109676391298279</v>
+        <v>0.9723394225659689</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.270177046372335</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.548987741410767</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.04766709757596</v>
+        <v>-4.391009519406735</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.072478161221626</v>
+        <v>0.935141192489316</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.3005259416869396</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.511585859553594</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.314671607848395</v>
+        <v>-4.65801402967917</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9713679194515976</v>
+        <v>0.8340309507192878</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.4948889797298882</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.400659599066771</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760816</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.415869389285568</v>
+        <v>-4.759211811116343</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9300927287732299</v>
+        <v>0.7927557600409201</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.5632977932752073</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.35881823283608</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.409358422671255</v>
+        <v>-4.75270084450203</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9302970769732717</v>
+        <v>0.7929601082409619</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.5632977932752073</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.356418194390397</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.390320294963958</v>
+        <v>-4.733662716794733</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9344370472644357</v>
+        <v>0.7971000785321258</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.6214814046064019</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.318032746799925</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421446926114577</v>
+        <v>-4.764789347945351</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.099568263742869</v>
+        <v>0.9622312950105589</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.6214814046064019</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.495614615738606</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.397987167089279</v>
+        <v>-4.778656109279269</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.109785496339121</v>
+        <v>0.9575179194631254</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4725063937754383</v>
+        <v>-0.6593393213402249</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.585832951223317</v>
+        <v>2.473733194684446</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789128</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.353182995549349</v>
+        <v>-4.733851937739339</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.133715695352019</v>
+        <v>0.9814481184760233</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4725063937754383</v>
+        <v>-0.6593393213402249</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.591841481620243</v>
+        <v>2.479741725081372</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.205440025314346</v>
+        <v>-4.586108967504336</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.271965531238042</v>
+        <v>1.119697954362046</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3046990365405552</v>
+        <v>-0.4915319641053417</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.771678543753195</v>
+        <v>2.659578787214323</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.307454707845568</v>
+        <v>-4.688123650035558</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.233953279757035</v>
+        <v>1.081685702881039</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3046990365405552</v>
+        <v>-0.4915319641053417</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.774472165284676</v>
+        <v>2.662372408745804</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394738</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.301302001792783</v>
+        <v>-4.681970943982773</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.237076710569807</v>
+        <v>1.084809133693811</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2985463304877709</v>
+        <v>-0.4853792580525574</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.778826137308005</v>
+        <v>2.666726380769133</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.318111299943285</v>
+        <v>-4.698780242133275</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.229433468049716</v>
+        <v>1.07716589117372</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3153556286382725</v>
+        <v>-0.502188556203059</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.767821035157815</v>
+        <v>2.655721278618942</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.255813301167163</v>
+        <v>-4.636482243357153</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.320688221356986</v>
+        <v>1.16842064448099</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3153556286382725</v>
+        <v>-0.502188556203059</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.834156588954635</v>
+        <v>2.722056832415763</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992197</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.054023103502005</v>
+        <v>-4.434692045691995</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.109985172812447</v>
+        <v>0.9577175959364512</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1173374364691182</v>
+        <v>-0.3041703640339046</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.661548376645526</v>
+        <v>2.549448620106654</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.980645006413269</v>
+        <v>-4.361313948603259</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.209626643970117</v>
+        <v>1.057359067094121</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0439593393803816</v>
+        <v>-0.2307922669451681</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.775865467220943</v>
+        <v>2.663765710682071</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319551</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.078385551038243</v>
+        <v>-4.459054493228233</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.185158162236171</v>
+        <v>1.032890585360175</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05984861751336179</v>
+        <v>-0.2466815450781483</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.780959636457199</v>
+        <v>2.668859879918327</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.83181903248939</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.254723311161172</v>
+        <v>-4.635392253351163</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.113159039011671</v>
+        <v>0.9608914621356748</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2361863776362912</v>
+        <v>-0.4230193052010777</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.673692961208113</v>
+        <v>2.561593204669241</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.8364116723978</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.178301264729245</v>
+        <v>-4.511328750870095</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.14221947562437</v>
+        <v>1.00900848116803</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2361863776362912</v>
+        <v>-0.4230193052010777</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.672184579248041</v>
+        <v>2.560084822709169</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024968</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.133928133090676</v>
+        <v>-4.466955619231526</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.159831595715234</v>
+        <v>1.026620601258894</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1918132459977226</v>
+        <v>-0.3786461735625091</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.698671325666619</v>
+        <v>2.586571569127746</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.125974162795904</v>
+        <v>-4.459001648936754</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.163013183833143</v>
+        <v>1.029802189376803</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1918132459977226</v>
+        <v>-0.3786461735625091</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.698671325666619</v>
+        <v>2.586571569127746</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.078318432234848</v>
+        <v>-4.411345918375698</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.18845723308537</v>
+        <v>1.05524623862903</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1441575154366669</v>
+        <v>-0.3309904430014534</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.733646521031057</v>
+        <v>2.621546764492185</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.977800273736094</v>
+        <v>-4.310827759876943</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.233556869859597</v>
+        <v>1.100345875403257</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.04363935693791238</v>
+        <v>-0.2304722845026989</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798849789505034</v>
+        <v>2.686750032966162</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.038466864138483</v>
+        <v>-4.371494350279333</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.196044906174513</v>
+        <v>1.062833911718173</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.125337673656446</v>
+        <v>-0.3121706012212325</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.736585471949786</v>
+        <v>2.624485715410914</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.993628462530085</v>
+        <v>-4.326655948670934</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.218077969428501</v>
+        <v>1.084866974972161</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1207942407115766</v>
+        <v>-0.307627168276363</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.743409234327336</v>
+        <v>2.631309477788465</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674312</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.094387098287084</v>
+        <v>-4.427414584427932</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.18193545475678</v>
+        <v>1.04872446030044</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.209619809438582</v>
+        <v>-0.3964527370033685</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.694274832722211</v>
+        <v>2.582175076183339</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.050184261201183</v>
+        <v>-4.383211747342032</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.205496192118977</v>
+        <v>1.072285197662637</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1654169723526815</v>
+        <v>-0.352249899917468</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.726676137501589</v>
+        <v>2.614576380962716</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.087163288864627</v>
+        <v>-4.420190775005475</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.189114581522847</v>
+        <v>1.055903587066508</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.128443070561351</v>
+        <v>-0.3152759981261375</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.747270479045635</v>
+        <v>2.635170722506762</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.107221367729467</v>
+        <v>-4.440248853870315</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.23233911515995</v>
+        <v>1.099128120703611</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.128443070561351</v>
+        <v>-0.3152759981261375</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.798518244228674</v>
+        <v>2.686418487689802</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.067290694551577</v>
+        <v>-4.400318180692425</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.24675208902536</v>
+        <v>1.11354109456902</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.08851239738346067</v>
+        <v>-0.2753453249482471</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.820917352729662</v>
+        <v>2.708817596190789</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.016258601829049</v>
+        <v>-4.349286087969897</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.262113154352641</v>
+        <v>1.128902159896301</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.03748030466093272</v>
+        <v>-0.2243132322257192</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.846484836601448</v>
+        <v>2.734385080062576</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162114</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.951034420701844</v>
+        <v>-4.284061906842692</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.305390230896228</v>
+        <v>1.172179236439888</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.02774387646627291</v>
+        <v>-0.1590890510985136</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.902806749370476</v>
+        <v>2.790706992831605</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.91360740063071</v>
+        <v>-4.246634886771558</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.316322011223962</v>
+        <v>1.183111016767623</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.03299541449545457</v>
+        <v>-0.1538375130693319</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.901918644487266</v>
+        <v>2.789818887948394</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.933719056665419</v>
+        <v>-4.162454217595043</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.309534141141319</v>
+        <v>1.218040076769469</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.04402275949287376</v>
+        <v>-0.09507345012304003</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.909791843816958</v>
+        <v>2.826334118047409</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393548</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.879974242238214</v>
+        <v>-4.108709403167838</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.491589837933411</v>
+        <v>1.400095773561562</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.05408606893333573</v>
+        <v>-0.08501014068257806</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.076387600502446</v>
+        <v>2.992929874732897</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714886</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.856182673632071</v>
+        <v>-4.084917834561695</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.621219374593685</v>
+        <v>1.529725310221836</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.07787763753947802</v>
+        <v>-0.06121857207643577</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.210775450883948</v>
+        <v>3.1273177251144</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.830098589368264</v>
+        <v>-4.058833750297887</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.623360984313067</v>
+        <v>1.531866919941218</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.07787763753947802</v>
+        <v>-0.06121857207643577</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.202483426897807</v>
+        <v>3.119025701128259</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.699806058438654</v>
+        <v>-3.928541219368277</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.673671192268691</v>
+        <v>1.582177127896842</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3144132620672128</v>
+        <v>0.175317052451299</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.342597997198228</v>
+        <v>3.259140271428679</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.796293177717119</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.690913597045371</v>
+        <v>-3.919648757974993</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.694782582552796</v>
+        <v>1.603288518180946</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3144132620672128</v>
+        <v>0.175317052451299</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.360152402925019</v>
+        <v>3.276694677155471</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702629</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.859389714015248</v>
+        <v>-4.088124874944871</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.619247183169428</v>
+        <v>1.527753118797579</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.286465426350632</v>
+        <v>0.1473692167347183</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.335238748899654</v>
+        <v>3.251781023130106</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539968</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.161590185153665</v>
+        <v>-3.390325346083288</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.879636691901923</v>
+        <v>1.788142627530074</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2161173669802213</v>
+        <v>0.07702115736430754</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.27429961046527</v>
+        <v>3.190841884695721</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389896</v>
+        <v>3.7847003793899</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.138869081470513</v>
+        <v>-3.367604242400135</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.879389155872089</v>
+        <v>1.78789509150024</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2161173669802213</v>
+        <v>0.07702115736430754</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.264963632962175</v>
+        <v>3.181505907192626</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534934</v>
+        <v>3.783234730534938</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.137144038180469</v>
+        <v>-3.365879199110092</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.038985299039275</v>
+        <v>1.947491234667426</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2178424102702651</v>
+        <v>0.07874620065435128</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.424904784787369</v>
+        <v>3.341447059017821</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401673</v>
+        <v>3.779962759401676</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.291925044958724</v>
+        <v>-3.520660205888347</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.01415071882162</v>
+        <v>1.922656654449771</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.184474736215789</v>
+        <v>0.04537852659987518</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.441962002848331</v>
+        <v>3.358504277078782</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557225</v>
+        <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.240489711574064</v>
+        <v>-3.469224872503687</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.031400208165029</v>
+        <v>1.93990614379318</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2359100696004486</v>
+        <v>0.09681385998453484</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.469498558868672</v>
+        <v>3.386040833099123</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088379</v>
+        <v>3.766702530088378</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.213538487247576</v>
+        <v>-3.442273648177199</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.052186851540366</v>
+        <v>1.960692787168517</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2507904156281678</v>
+        <v>0.111694206012254</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.488432920130045</v>
+        <v>3.404975194360496</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541369</v>
+        <v>3.768081101541371</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.178502002147465</v>
+        <v>-3.578226656233515</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.250304577725371</v>
+        <v>2.09041471609095</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2507904156281678</v>
+        <v>0.111694206012254</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.672536052275004</v>
+        <v>3.589078326505456</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.200910119952337</v>
+        <v>-3.600634774038387</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.233458025506414</v>
+        <v>2.073568163871994</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2507904156281678</v>
+        <v>0.111694206012254</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.664652747177997</v>
+        <v>3.581195021408449</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912294</v>
+        <v>3.719147660912297</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.348915887431736</v>
+        <v>-3.748640541517787</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.176309718064292</v>
+        <v>2.016419856429872</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1640634067646263</v>
+        <v>0.02496719714871254</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.61467054140951</v>
+        <v>3.531212815639962</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729481318919242</v>
+        <v>3.72948131891924</v>
       </c>
       <c r="C2006" t="n">
         <v>3.572486215072581</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.358356813320266</v>
+        <v>-3.613026489959041</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.228787065430728</v>
+        <v>2.126919194775218</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2864905243080177</v>
+        <v>0.1855460606467033</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.744380529657392</v>
+        <v>3.683813851460603</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.758348826980376</v>
+        <v>3.482741898739693</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.692841438568102</v>
+        <v>3.564379648598656</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.358356813320266</v>
+        <v>-3.613026489959041</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.228787065430728</v>
+        <v>2.126919194775218</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.2864905243080177</v>
+        <v>0.1855460606467033</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.68590523555447</v>
+        <v>3.557443445585024</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240626.xlsx
+++ b/tame_output/ON/bt/strategyON_20240626.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.9%</t>
+          <t>451.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.9%</t>
+          <t>-522.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>162.7%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.5%</t>
+          <t>-163.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>-211.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.7%</t>
+          <t>-171.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-205.4%</t>
+          <t>-199.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-74.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2007"/>
+  <dimension ref="A1:G2006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.420182573667817</v>
+        <v>-7.352766700288008</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1401905492431355</v>
+        <v>0.1671568985950591</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.664453974394887</v>
+        <v>-7.597038101015078</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.05274067962098661</v>
+        <v>0.07970702897291027</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.869704993631647</v>
+        <v>-7.802289120251838</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03326016292802203</v>
+        <v>-0.006293813576098817</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.033284871816031</v>
+        <v>-7.965868998436221</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1002871941467749</v>
+        <v>-0.07332084479485124</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.329946213626229</v>
+        <v>-8.262530340246419</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.215172754941646</v>
+        <v>-0.1882064055897223</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.516665921935532</v>
+        <v>-8.449250048555722</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2938869427997703</v>
+        <v>-0.2669205934478462</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.899667310678163</v>
+        <v>-8.832251437298353</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4471895996184068</v>
+        <v>-0.4202232502664831</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.081537101663198</v>
+        <v>-9.014121228283388</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5173660000409908</v>
+        <v>-0.4903996506890667</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.441067424167199</v>
+        <v>-9.37365155078739</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6558278257445411</v>
+        <v>-0.628861476392617</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.491416487621422</v>
+        <v>-9.424000614241612</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6680514311690522</v>
+        <v>-0.6410850818171285</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.589035765042818</v>
+        <v>-9.521619891663008</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7040573915158421</v>
+        <v>-0.677091042163918</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.73656185304846</v>
+        <v>-9.669145979668651</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7601742703965271</v>
+        <v>-0.733207921044603</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.940820028378324</v>
+        <v>-9.873404154998514</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.83636434340983</v>
+        <v>-0.8093979940579059</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.01515300463849</v>
+        <v>-9.947737131258679</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8616149794294601</v>
+        <v>-0.834648630077536</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.94168317297104</v>
+        <v>-9.87426729959123</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.816855345269059</v>
+        <v>-0.7898889959171349</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.11680759035758</v>
+        <v>-10.04939171697777</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8723498914761594</v>
+        <v>-0.8453835421242353</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.35125968437207</v>
+        <v>-10.28384381099226</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9733498939835514</v>
+        <v>-0.9463835446316273</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.45563441539852</v>
+        <v>-10.38821854201871</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.021771977168106</v>
+        <v>-0.9948056278161821</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.50842057099885</v>
+        <v>-10.44100469761904</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.04177064956968</v>
+        <v>-1.014804300217756</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.63445736436713</v>
+        <v>-10.56704149098733</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.089491638287881</v>
+        <v>-1.062525288935957</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.58244185039832</v>
+        <v>-10.51502597701851</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.064695097013955</v>
+        <v>-1.037728747662031</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.72411369212244</v>
+        <v>-10.65669781874263</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.122839060602345</v>
+        <v>-1.095872711250421</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.67452284769761</v>
+        <v>-10.6071069743178</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.087949312667539</v>
+        <v>-1.060982963315615</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.66171545469283</v>
+        <v>-10.59429958131302</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.095877489112313</v>
+        <v>-1.068911139760389</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.43587030197342</v>
+        <v>-10.36845442859361</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9959603549883398</v>
+        <v>-0.9689940056364157</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.31129164563583</v>
+        <v>-10.24387577225602</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9449897478972447</v>
+        <v>-0.9180233985453197</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.36418693368012</v>
+        <v>-10.29677106030031</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9635140889528513</v>
+        <v>-0.9365477396009263</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.29205375839224</v>
+        <v>-10.22463788501243</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9289271145990625</v>
+        <v>-0.9019607652471375</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.22068736578259</v>
+        <v>-10.15327149240278</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9101178199490683</v>
+        <v>-0.8831514705971442</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232416</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.12722833179737</v>
+        <v>-10.05981245841755</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8826176876678864</v>
+        <v>-0.8556513383159614</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436232</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.859986530928968</v>
+        <v>-9.792570657549156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7775555278199011</v>
+        <v>-0.7505891784679766</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311952</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.762079492252477</v>
+        <v>-9.694663618872665</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7386930273227654</v>
+        <v>-0.7117266779708409</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097247</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.738125951276519</v>
+        <v>-9.670710077896707</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7284431047868889</v>
+        <v>-0.7014767554349643</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017775</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.474066012953722</v>
+        <v>-9.406650139573911</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6360794456195222</v>
+        <v>-0.6091130962675977</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839729</v>
+        <v>3.83325274783973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.766986389448885</v>
+        <v>-8.699570516069073</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3560346298778883</v>
+        <v>-0.3290682805259637</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.726802091082694</v>
+        <v>-8.659386217702883</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3396172866435707</v>
+        <v>-0.3126509372916462</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.563402220143331</v>
+        <v>-8.495986346763519</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2748905170470684</v>
+        <v>-0.2479241676951438</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.329920997913732</v>
+        <v>-8.26250512453392</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1735735993173764</v>
+        <v>-0.1466072499654514</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.180254606906217</v>
+        <v>-8.112838733526406</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1165992532273297</v>
+        <v>-0.08963290387540512</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.04797913327533</v>
+        <v>-7.980563259895519</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06832157702794772</v>
+        <v>-0.04135522767602362</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.892240800715588</v>
+        <v>-7.824824927335778</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.003211183316414346</v>
+        <v>0.0237551660355102</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.643241002032007</v>
+        <v>-7.575825128652196</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1092950773806769</v>
+        <v>0.136261426732601</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.748830991805112</v>
+        <v>-7.681415118425301</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06091684812778375</v>
+        <v>-0.03395049877585921</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987906</v>
+        <v>3.77042258398791</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.767565893923709</v>
+        <v>-7.700150020543898</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01986646709813611</v>
+        <v>0.007099882253788437</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.619625852516109</v>
+        <v>-7.552209979136299</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08056937322326396</v>
+        <v>-0.05360302387133942</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.566656330262121</v>
+        <v>-7.49924045688231</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06809555057514682</v>
+        <v>-0.04112920122322228</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.52310792349143</v>
+        <v>-7.45569205011162</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.0576367999619638</v>
+        <v>-0.03067045061003926</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.280959530037572</v>
+        <v>-7.213543656657762</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05368491180072255</v>
+        <v>0.08065126115264709</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.172700392915051</v>
+        <v>-7.10528451953524</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09152068710892625</v>
+        <v>0.1184870364608508</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.04940925809792</v>
+        <v>-6.981993384718109</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1383352350463558</v>
+        <v>0.1653015843982799</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919913</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.028260059194476</v>
+        <v>-6.960844185814666</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1544958928450582</v>
+        <v>0.1814622421969823</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.784494617211032</v>
+        <v>-6.717078743831221</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2477827779854866</v>
+        <v>0.2747491273374107</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.682731796933737</v>
+        <v>-6.615315923553927</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2906122200164205</v>
+        <v>0.3175785693683446</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279188</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.432881402984663</v>
+        <v>-6.365465529604852</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3832944525797526</v>
+        <v>0.4102608019316767</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.256989310517231</v>
+        <v>-6.189573437137419</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4572504130873742</v>
+        <v>0.4842167624392988</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.085542847494767</v>
+        <v>-6.018126974114955</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5391565043509132</v>
+        <v>0.5661228537028378</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.011253281756428</v>
+        <v>-5.943837408376616</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5678928082625458</v>
+        <v>0.5948591576144704</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883078</v>
+        <v>3.764617879883081</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.947617539522494</v>
+        <v>-5.880201666142682</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5980419062104367</v>
+        <v>0.6250082555623617</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.798814771074792</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.836190780196573</v>
+        <v>-5.768774906816762</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6238068687246008</v>
+        <v>0.6507732180765253</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976948842423</v>
+        <v>3.797694884242303</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.595760283391713</v>
+        <v>-5.528344410011901</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7217221440714221</v>
+        <v>0.7486884934233466</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936769</v>
+        <v>3.821593509367694</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.523517715220518</v>
+        <v>-5.456101841840707</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7545484851747202</v>
+        <v>0.7815148345266447</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879975</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.47051939293913</v>
+        <v>-5.403103519559319</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7764263980046153</v>
+        <v>0.8033927473565399</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502344</v>
+        <v>3.848616626502347</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.361714507459403</v>
+        <v>-5.294298634079592</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8169464234164998</v>
+        <v>0.8439127727684244</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675946</v>
+        <v>3.818668951675948</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.141693709422393</v>
+        <v>-5.074277836042581</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9065337796419182</v>
+        <v>0.9335001289938427</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539957</v>
+        <v>3.843274527539959</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.008826020359115</v>
+        <v>-4.941410146979304</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9755750380690524</v>
+        <v>1.002541387420977</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496268</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.888652936994617</v>
+        <v>-4.821237063614805</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.024790115855154</v>
+        <v>1.051756465207078</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551577005</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.743980791894879</v>
+        <v>-4.676564918515068</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.092747076456489</v>
+        <v>1.119713425808413</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.73583922294211</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.803855619252571</v>
+        <v>-4.73643974587276</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.054834636914837</v>
+        <v>1.081800986266762</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674522</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.717056121473563</v>
+        <v>-4.649640248093752</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.111954929349007</v>
+        <v>1.138921278700932</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430701</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.719525827935369</v>
+        <v>-4.652109954555558</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.111039448137697</v>
+        <v>1.138005797489621</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003606</v>
+        <v>3.74322019600361</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.787896014259379</v>
+        <v>-4.720480140879568</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.094698296082794</v>
+        <v>1.121664645434719</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508374</v>
+        <v>3.714179139508378</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.801684067106426</v>
+        <v>-4.734268193726614</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.079619783575867</v>
+        <v>1.106586132927792</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417709</v>
+        <v>3.710906731417713</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.832677226435131</v>
+        <v>-4.76526135305532</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8919320848847718</v>
+        <v>0.9188984342366964</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205908</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.657202966642663</v>
+        <v>-4.589787093262851</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.966689020793547</v>
+        <v>0.9936553701454718</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322545</v>
+        <v>3.765024323225453</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.768139219283912</v>
+        <v>-4.7007233459041</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8980565484982546</v>
+        <v>0.9250228978501793</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.734475673811629</v>
+        <v>-4.667059800431818</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.914653351907073</v>
+        <v>0.9416197012589977</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264171</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.674623054607906</v>
+        <v>-4.607207181228095</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9487667860206948</v>
+        <v>0.9757331353726193</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742308</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.588379591581528</v>
+        <v>-4.520963718201717</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9782104418051061</v>
+        <v>1.005176791157031</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.633686410980508</v>
+        <v>-4.566270537600697</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9518634894900397</v>
+        <v>0.9788298388419643</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.7535711658032</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.662719515682809</v>
+        <v>-4.595303642302998</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9408021206422208</v>
+        <v>0.9677684699941453</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809506</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.56990903423195</v>
+        <v>-4.502493160852138</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9071990051139303</v>
+        <v>0.934165354465855</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.614298503561377</v>
+        <v>-4.546882630181566</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8913166933067602</v>
+        <v>0.9182830426586848</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472742</v>
+        <v>3.721077195472746</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.501627285325127</v>
+        <v>-4.434211411945316</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9314608891129832</v>
+        <v>0.9584272384649077</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798542</v>
+        <v>3.743047603798545</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.389250284142454</v>
+        <v>-4.321834410762643</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9819029854167196</v>
+        <v>1.008869334768644</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049887</v>
+        <v>3.689597840498873</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.417030682043807</v>
+        <v>-4.349614808663995</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9822880280247177</v>
+        <v>1.009254377376642</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705334</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.500031963069086</v>
+        <v>-4.432616089689274</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7874432356152594</v>
+        <v>0.814409584967184</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729275</v>
+        <v>3.682716310729278</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.608646041512417</v>
+        <v>-4.541230168132605</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8641472649571325</v>
+        <v>0.8911136143090572</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190774</v>
+        <v>3.733012441190778</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.573237003264274</v>
+        <v>-4.505821129884462</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8928239063587127</v>
+        <v>0.9197902557106372</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913435</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.534853340706123</v>
+        <v>-4.467437467326311</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9055968127243417</v>
+        <v>0.9325631620762664</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532492</v>
+        <v>3.751147197532496</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.357737010670957</v>
+        <v>-4.290321137291145</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9731723735837101</v>
+        <v>1.000138722935635</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.74132844879391</v>
+        <v>3.741328448793913</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.402829255504503</v>
+        <v>-4.335413382124691</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.955818867412205</v>
+        <v>0.9827852167641296</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011246</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.345995305886128</v>
+        <v>-4.156037960885923</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9723394225659689</v>
+        <v>1.048322360566051</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.270177046372335</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.548987741410767</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.71699171898224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.391009519406735</v>
+        <v>-4.201052174406529</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.935141192489316</v>
+        <v>1.011124130489399</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3005259416869396</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.511585859553594</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509546</v>
+        <v>3.737026608509549</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.65801402967917</v>
+        <v>-4.468056684678964</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8340309507192878</v>
+        <v>0.9100138887193703</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4948889797298882</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.400659599066771</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760816</v>
+        <v>3.70230945476082</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.759211811116343</v>
+        <v>-4.569254466116137</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7927557600409201</v>
+        <v>0.8687386980410026</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5632977932752073</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.35881823283608</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815464</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.75270084450203</v>
+        <v>-4.562743499501824</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7929601082409619</v>
+        <v>0.8689430462410443</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5632977932752073</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.356418194390397</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.733662716794733</v>
+        <v>-4.543705371794527</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7971000785321258</v>
+        <v>0.8730830165322081</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6214814046064019</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.318032746799925</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.764789347945351</v>
+        <v>-4.574832002945145</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9622312950105589</v>
+        <v>1.038214233010641</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6214814046064019</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.495614615738606</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.778656109279269</v>
+        <v>-4.588698764279063</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9575179194631254</v>
+        <v>1.033500857463208</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6593393213402249</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.473733194684446</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789128</v>
+        <v>3.787425580789131</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.733851937739339</v>
+        <v>-4.543894592739133</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9814481184760233</v>
+        <v>1.057431056476106</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6593393213402249</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.479741725081372</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519918</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.586108967504336</v>
+        <v>-4.396151622504131</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.119697954362046</v>
+        <v>1.195680892362128</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4915319641053417</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.659578787214323</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.80224592918118</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.688123650035558</v>
+        <v>-4.498166305035352</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.081685702881039</v>
+        <v>1.157668640881121</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4915319641053417</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.662372408745804</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394738</v>
+        <v>3.80560898539474</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.681970943982773</v>
+        <v>-4.492013598982568</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.084809133693811</v>
+        <v>1.160792071693893</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4853792580525574</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.666726380769133</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.698780242133275</v>
+        <v>-4.508822897133069</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.07716589117372</v>
+        <v>1.153148829173803</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.502188556203059</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.655721278618942</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.636482243357153</v>
+        <v>-4.446524898356947</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.16842064448099</v>
+        <v>1.244403582481072</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.502188556203059</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.722056832415763</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992197</v>
+        <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.434692045691995</v>
+        <v>-4.244734700691789</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9577175959364512</v>
+        <v>1.033700533936534</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3041703640339046</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.549448620106654</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.361313948603259</v>
+        <v>-4.171356603603053</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.057359067094121</v>
+        <v>1.133342005094203</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2307922669451681</v>
+        <v>-0.08018922680401847</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.663765710682071</v>
+        <v>2.754127534766761</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319551</v>
+        <v>3.819063300319556</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.459054493228233</v>
+        <v>-4.269097148228028</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.032890585360175</v>
+        <v>1.108873523360257</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2466815450781483</v>
+        <v>-0.09607850493699865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.668859879918327</v>
+        <v>2.759221704003016</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248939</v>
+        <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.635392253351163</v>
+        <v>-4.445434908350957</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9608914621356748</v>
+        <v>1.036874400135757</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4230193052010777</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.561593204669241</v>
+        <v>2.65195502875393</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.8364116723978</v>
+        <v>3.836411672397804</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.511328750870095</v>
+        <v>-4.36901286191903</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.00900848116803</v>
+        <v>1.065934836748456</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4230193052010777</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.560084822709169</v>
+        <v>2.650446646793859</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024968</v>
+        <v>3.833513460316259</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.466955619231526</v>
+        <v>-4.324639730280461</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.026620601258894</v>
+        <v>1.08354695683932</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3786461735625091</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.586571569127746</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821562117105973</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.459001648936754</v>
+        <v>-4.201805509393294</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.029802189376803</v>
+        <v>1.127074439332778</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3786461735625091</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.586571569127746</v>
+        <v>2.671327187351027</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833011148190332</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.411345918375698</v>
+        <v>-4.154149778832238</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.05524623862903</v>
+        <v>1.152518488585004</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3309904430014534</v>
+        <v>-0.1803874028603038</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.621546764492185</v>
+        <v>2.706302382715465</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326878</v>
+        <v>3.822678210569624</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.310827759876943</v>
+        <v>-4.053631620333483</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.100345875403257</v>
+        <v>1.197618125359231</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2304722845026989</v>
+        <v>-0.07986924436154924</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.686750032966162</v>
+        <v>2.771505651189442</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314554</v>
+        <v>3.828808877557299</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.371494350279333</v>
+        <v>-4.114298210735873</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.062833911718173</v>
+        <v>1.160106161674147</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3121706012212325</v>
+        <v>-0.1615675610800829</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.624485715410914</v>
+        <v>2.709241333634194</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.326655948670934</v>
+        <v>-4.069459809127475</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.084866974972161</v>
+        <v>1.182139224928135</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.307627168276363</v>
+        <v>-0.1570241281352134</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.631309477788465</v>
+        <v>2.716065096011744</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.427414584427932</v>
+        <v>-4.170218444884473</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.04872446030044</v>
+        <v>1.145996710256414</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3964527370033685</v>
+        <v>-0.2458496968622189</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.582175076183339</v>
+        <v>2.666930694406619</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.383211747342032</v>
+        <v>-4.126015607798572</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.072285197662637</v>
+        <v>1.169557447618611</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.352249899917468</v>
+        <v>-0.2016468597763184</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.614576380962716</v>
+        <v>2.699331999185997</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.420190775005475</v>
+        <v>-4.162994635462015</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.055903587066508</v>
+        <v>1.153175837022482</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3152759981261375</v>
+        <v>-0.1646729579849879</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.635170722506762</v>
+        <v>2.719926340730042</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.440248853870315</v>
+        <v>-4.183052714326855</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.099128120703611</v>
+        <v>1.196400370659585</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.3152759981261375</v>
+        <v>-0.1646729579849879</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.686418487689802</v>
+        <v>2.771174105913082</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.400318180692425</v>
+        <v>-4.143122041148965</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.11354109456902</v>
+        <v>1.210813344524994</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2753453249482471</v>
+        <v>-0.1247422848070975</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.708817596190789</v>
+        <v>2.793573214414069</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.349286087969897</v>
+        <v>-4.092089948426437</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.128902159896301</v>
+        <v>1.226174409852276</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2243132322257192</v>
+        <v>-0.07371019208456958</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.734385080062576</v>
+        <v>2.819140698285856</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.284061906842692</v>
+        <v>-4.026865767299232</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.172179236439888</v>
+        <v>1.269451486395863</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1590890510985136</v>
+        <v>-0.008486010957363954</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.790706992831605</v>
+        <v>2.875462611054885</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.246634886771558</v>
+        <v>-3.989438747228098</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.183111016767623</v>
+        <v>1.280383266723596</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1538375130693319</v>
+        <v>-0.003234472928182297</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.789818887948394</v>
+        <v>2.874574506171674</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749925</v>
+        <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.162454217595043</v>
+        <v>-4.009550403262806</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.218040076769469</v>
+        <v>1.273595396640954</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.09507345012304003</v>
+        <v>0.0077928720692369</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.826334118047409</v>
+        <v>2.882447705501366</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.108709403167838</v>
+        <v>-3.955805588835601</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.400095773561562</v>
+        <v>1.455651093433046</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.08501014068257806</v>
+        <v>0.01785618150969887</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.992929874732897</v>
+        <v>3.049043462186853</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714889</v>
+        <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.084917834561695</v>
+        <v>-3.932014020229459</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.529725310221836</v>
+        <v>1.58528063009332</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.06121857207643577</v>
+        <v>0.04164775011584115</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.1273177251144</v>
+        <v>3.183431312568356</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756015</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.058833750297887</v>
+        <v>-3.905929935965651</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.531866919941218</v>
+        <v>1.587422239812702</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.06121857207643577</v>
+        <v>0.04164775011584115</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.119025701128259</v>
+        <v>3.175139288582215</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654189</v>
+        <v>3.803397818896934</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.928541219368277</v>
+        <v>-3.775637405036041</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.582177127896842</v>
+        <v>1.637732447768326</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.175317052451299</v>
+        <v>0.278183374643576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.259140271428679</v>
+        <v>3.315253858882635</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717119</v>
+        <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.919648757974993</v>
+        <v>-3.766744943642758</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.603288518180946</v>
+        <v>1.658843838052431</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.175317052451299</v>
+        <v>0.278183374643576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.276694677155471</v>
+        <v>3.332808264609427</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702629</v>
+        <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.088124874944871</v>
+        <v>-3.935221060612636</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.527753118797579</v>
+        <v>1.583308438669063</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1473692167347183</v>
+        <v>0.2502355389269952</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.251781023130106</v>
+        <v>3.307894610584063</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539971</v>
+        <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.144629190277137</v>
+        <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.390325346083288</v>
+        <v>-3.237421531751052</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.788142627530074</v>
+        <v>1.843697947401559</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.07702115736430754</v>
+        <v>0.1798874795565845</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.190841884695721</v>
+        <v>3.246955472149678</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.7847003793899</v>
+        <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.135293212774041</v>
+        <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.367604242400135</v>
+        <v>-3.2147004280679</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.78789509150024</v>
+        <v>1.843450411371724</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.07702115736430754</v>
+        <v>0.1798874795565845</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.181505907192626</v>
+        <v>3.237619494646582</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534938</v>
+        <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.29419933862521</v>
+        <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.365879199110092</v>
+        <v>-3.212975384777856</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.947491234667426</v>
+        <v>2.003046554538911</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.07874620065435128</v>
+        <v>0.1816125228466282</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.341447059017821</v>
+        <v>3.397560646471778</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401676</v>
+        <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.331277161118857</v>
+        <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.520660205888347</v>
+        <v>-3.367756391556111</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.922656654449771</v>
+        <v>1.978211974321256</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.04537852659987518</v>
+        <v>0.1482448487921521</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.358504277078782</v>
+        <v>3.414617864532739</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.327952517108402</v>
+        <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.469224872503687</v>
+        <v>-3.316321058171452</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.93990614379318</v>
+        <v>1.995461463664665</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.09681385998453484</v>
+        <v>0.1996801821768118</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.386040833099123</v>
+        <v>3.442154420553079</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088378</v>
+        <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.337958670753144</v>
+        <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.442273648177199</v>
+        <v>-3.289369833844964</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.960692787168517</v>
+        <v>2.016248107040001</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.111694206012254</v>
+        <v>0.2145605282045309</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.404975194360496</v>
+        <v>3.461088781814452</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541371</v>
+        <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.522061802898103</v>
+        <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.578226656233515</v>
+        <v>-3.42532284190128</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.09041471609095</v>
+        <v>2.145970035962434</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.111694206012254</v>
+        <v>0.2145605282045309</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.589078326505456</v>
+        <v>3.645191913959412</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471686</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.514178497801097</v>
+        <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.600634774038387</v>
+        <v>-3.447730959706152</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.073568163871994</v>
+        <v>2.129123483743479</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.111694206012254</v>
+        <v>0.2145605282045309</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.581195021408449</v>
+        <v>3.637308608862405</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912297</v>
+        <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.516232497350734</v>
+        <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.748640541517787</v>
+        <v>-3.595736727185551</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.016419856429872</v>
+        <v>2.071975176301356</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.02496719714871254</v>
+        <v>0.1278335193409895</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.531212815639962</v>
+        <v>3.587326403093918</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,45 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72948131891924</v>
+        <v>3.729125055920937</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.572486215072581</v>
+        <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.613026489959041</v>
+        <v>-3.605177653074081</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.126919194775218</v>
+        <v>2.124452523667792</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1855460606467033</v>
+        <v>0.2502606368843809</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.683813851460603</v>
-      </c>
-    </row>
-    <row r="2007">
-      <c r="A2007" s="2" t="n">
-        <v>45469</v>
-      </c>
-      <c r="B2007" t="n">
-        <v>3.482741898739693</v>
-      </c>
-      <c r="C2007" t="n">
-        <v>3.564379648598656</v>
-      </c>
-      <c r="D2007" t="n">
-        <v>-3.613026489959041</v>
-      </c>
-      <c r="E2007" t="n">
-        <v>2.126919194775218</v>
-      </c>
-      <c r="F2007" t="n">
-        <v>0.1855460606467033</v>
-      </c>
-      <c r="G2007" t="n">
-        <v>3.557443445585024</v>
+        <v>3.7170363913418</v>
       </c>
     </row>
   </sheetData>
